--- a/source/09/genai_rpa.xlsx
+++ b/source/09/genai_rpa.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ai_x\source\09\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5B72540-6C64-468C-BE9D-DD5B2F35BB27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DCE294E-0E67-49C7-BE6A-257F2287340D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38955" yWindow="3885" windowWidth="17280" windowHeight="8970" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2652" yWindow="2652" windowWidth="17280" windowHeight="8880" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="origin_report" sheetId="26" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="prev_report" sheetId="238" r:id="rId3"/>
     <sheet name="now_report_en" sheetId="206" r:id="rId4"/>
     <sheet name="now_list" sheetId="204" r:id="rId5"/>
-    <sheet name="prev_list" sheetId="237" r:id="rId6"/>
+    <sheet name="prev_list" sheetId="239" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="184">
   <si>
     <t>OOO 일일 동향 보고서</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -240,18 +240,6 @@
   </si>
   <si>
     <t>트릿/스틱</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;포켄스&lt;/b&gt; 덴티페어리 SS 디스펜서 (124p) 강아지 덴탈껌</t>
-  </si>
-  <si>
-    <t>https://www.11st.co.kr/connect/Gateway.tmall?method=Xsite&amp;prdNo=7898487960&amp;tid=1000000061</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5557929/55579294213.jpg</t>
-  </si>
-  <si>
-    <t>페슬러</t>
   </si>
   <si>
     <t>강아지껌 &lt;b&gt;포켄스&lt;/b&gt; 덴티 페어리 75g L 특식 영양식</t>
@@ -378,6 +366,246 @@
 - 협찬: 다양한 시상품 즉석추첨 배포  
 - 참석자: 회원 약 100명(추정)</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고급 남자 &lt;b&gt;노트북&lt;/b&gt; 책가방 학생 백팩 USB 포트 가방</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12045161943</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958967/89589672642.jpg</t>
+  </si>
+  <si>
+    <t>생활백화점1</t>
+  </si>
+  <si>
+    <t>패션잡화</t>
+  </si>
+  <si>
+    <t>남성가방</t>
+  </si>
+  <si>
+    <t>백팩</t>
+  </si>
+  <si>
+    <t>[ 437325 ] Hobbywing 30109003 퀵런 방수 8bl150 G2 Esc</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12045161239</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958967/89589671938.jpg</t>
+  </si>
+  <si>
+    <t>아쥬어 브라운 로우즈</t>
+  </si>
+  <si>
+    <t>디지털/가전</t>
+  </si>
+  <si>
+    <t>노트북액세서리</t>
+  </si>
+  <si>
+    <t>기타노트북액세서리</t>
+  </si>
+  <si>
+    <t>샤오미 패드 5 패드5 고성능 BN4E 4900mAh용 &lt;b&gt;노트북&lt;/b&gt; 배터리</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12045159342</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958967/89589670041.jpg</t>
+  </si>
+  <si>
+    <t>씨케이물류</t>
+  </si>
+  <si>
+    <t>공구</t>
+  </si>
+  <si>
+    <t>전기용품</t>
+  </si>
+  <si>
+    <t>기타 전기용품</t>
+  </si>
+  <si>
+    <t>인스팩 80 LED 셀카 조명 아이폰용 휴대용 휴대폰 클립 틱톡 영상 촬영용 줌 통화 컴퓨터용 고출력 충전식 3단계 모드 &lt;b&gt;노트북&lt;/b&gt; 회의용 핑크 Black</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12045159407</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958967/89589670106.jpg</t>
+  </si>
+  <si>
+    <t>단비모터스2</t>
+  </si>
+  <si>
+    <t>카메라/캠코더용품</t>
+  </si>
+  <si>
+    <t>필름/관련용품</t>
+  </si>
+  <si>
+    <t>기타필름/관련용품</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;노트북&lt;/b&gt; 배터리 Asus 아수스 A32-N55 N45 N45SF N55E N75S N45E N45SJ N55S N75SF N45F N45SL N55SF N75SJ N45J</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12045158778</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958966/89589669476.jpg</t>
+  </si>
+  <si>
+    <t>L15L4A02 32WH &lt;b&gt;노트북&lt;/b&gt; 배터리 레노버 Idea패드 V110-15AST V310-14ISK V510-14IKB 15IKB E42-80 E52-80 L15C4A02 L15C4</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12045158507</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958966/89589669206.jpg</t>
+  </si>
+  <si>
+    <t>A7 가죽 소형 &lt;b&gt;노트북&lt;/b&gt; 포켓 메모장 플래너 메모 저널 학교 비즈 사무실 일정 참고 도서 세트 케이스 커버 1</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12045157921</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958966/89589668620.jpg</t>
+  </si>
+  <si>
+    <t>픽스테디</t>
+  </si>
+  <si>
+    <t>문구/사무용품</t>
+  </si>
+  <si>
+    <t>다이어리/플래너</t>
+  </si>
+  <si>
+    <t>스케줄러/플래너</t>
+  </si>
+  <si>
+    <t>4in 1 &lt;b&gt;노트북&lt;/b&gt; 어댑터 USB2.0 Type-C to RJ45 랜 네트워크 카드 4포트 허브 10GBit/s 데스크탑 컴퓨터 PC용</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12045157913</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958966/89589668612.jpg</t>
+  </si>
+  <si>
+    <t>스마트랩팩토리구산</t>
+  </si>
+  <si>
+    <t>PC액세서리</t>
+  </si>
+  <si>
+    <t>기타PC액세서리</t>
+  </si>
+  <si>
+    <t>에이서 E5-522 적용 배터리 &lt;b&gt;노트북&lt;/b&gt; 722G ES1-420/421 P257 P258 P277</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12045157888</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958966/89589668587.jpg</t>
+  </si>
+  <si>
+    <t>POLONO 무선 휴대용 열전사 프린터 D810 블루투스 8.5x11 화이트 iOS 안드로이드 &lt;b&gt;노트북&lt;/b&gt; 호환</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12045157651</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958966/89589668350.jpg</t>
+  </si>
+  <si>
+    <t>섬이픽</t>
+  </si>
+  <si>
+    <t>주변기기</t>
+  </si>
+  <si>
+    <t>프린터</t>
+  </si>
+  <si>
+    <t>라벨프린터</t>
+  </si>
+  <si>
+    <t>2PCS &lt;b&gt;노트북&lt;/b&gt; 스피커 23W 4R 8R 4020 2040 시끄러운 스피커 48 옴 123W 40x20MM 두께 8.5MM</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12045157544</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958966/89589668243.jpg</t>
+  </si>
+  <si>
+    <t>ITK</t>
+  </si>
+  <si>
+    <t>PC부품</t>
+  </si>
+  <si>
+    <t>튜닝용품</t>
+  </si>
+  <si>
+    <t>기타튜닝용품</t>
+  </si>
+  <si>
+    <t>기본 &lt;b&gt;노트북&lt;/b&gt;수납가방 오피스백팩 학생가방 데일리백팩</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12045157488</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958966/89589668187.jpg</t>
+  </si>
+  <si>
+    <t>집콕 자취필수템</t>
+  </si>
+  <si>
+    <t>후지츠용 배터리 &lt;b&gt;노트북&lt;/b&gt; V5515 V5535 V5555 V6515 V6555 La-1703 V5505</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12045157389</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958966/89589668088.jpg</t>
+  </si>
+  <si>
+    <t>러시아어 &lt;b&gt;노트북&lt;/b&gt; 키보드 레노보 V570 V570C V575 Z570 Z575 B570 B570A B570E V580C B570G B575 B575A B575E B590 B590A</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12045157402</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958966/89589668101.jpg</t>
+  </si>
+  <si>
+    <t>뉴글로벌스토어</t>
+  </si>
+  <si>
+    <t>키보드</t>
+  </si>
+  <si>
+    <t>무선키보드</t>
+  </si>
+  <si>
+    <t>LMDTK &lt;b&gt;노트북&lt;/b&gt; 배터리 도시바 Satellite L55-A5284NR L55-A5299 L55Dt-A5254 L50 L50-A L45 L45D L55 L55t L55D P50 P</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12045156949</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958966/89589667648.jpg</t>
   </si>
 </sst>
 </file>
@@ -881,7 +1109,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.4">
@@ -891,7 +1119,7 @@
     </row>
     <row r="5" spans="1:1" ht="38.4" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -902,7 +1130,7 @@
     </row>
     <row r="8" spans="1:1" s="3" customFormat="1" ht="96" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -930,7 +1158,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.4">
@@ -940,7 +1168,7 @@
     </row>
     <row r="5" spans="1:1" ht="38.4" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -951,7 +1179,7 @@
     </row>
     <row r="8" spans="1:1" s="3" customFormat="1" ht="57.6" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1012,7 +1240,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.4">
@@ -1067,37 +1295,34 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E2">
-        <v>10990</v>
+        <v>74540</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="H2">
-        <v>55580027908</v>
+        <v>89589672642</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="L2" t="s">
-        <v>19</v>
+        <v>108</v>
       </c>
       <c r="M2" t="s">
-        <v>20</v>
+        <v>109</v>
       </c>
       <c r="N2" t="s">
-        <v>30</v>
-      </c>
-      <c r="O2" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.4">
@@ -1105,37 +1330,34 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="E3">
-        <v>34700</v>
+        <v>170720</v>
       </c>
       <c r="G3" t="s">
-        <v>18</v>
+        <v>114</v>
       </c>
       <c r="H3">
-        <v>55579876708</v>
+        <v>89589671938</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
       <c r="L3" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="M3" t="s">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="N3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O3" t="s">
-        <v>31</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.4">
@@ -1143,22 +1365,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="E4">
-        <v>69400</v>
+        <v>32270</v>
       </c>
       <c r="G4" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="H4">
-        <v>55579859939</v>
+        <v>89589670041</v>
       </c>
       <c r="I4">
         <v>2</v>
@@ -1167,13 +1389,13 @@
         <v>19</v>
       </c>
       <c r="M4" t="s">
-        <v>20</v>
+        <v>122</v>
       </c>
       <c r="N4" t="s">
-        <v>30</v>
+        <v>123</v>
       </c>
       <c r="O4" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.4">
@@ -1181,37 +1403,37 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="E5">
-        <v>18200</v>
+        <v>41510</v>
       </c>
       <c r="G5" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="H5">
-        <v>55579843217</v>
+        <v>89589670106</v>
       </c>
       <c r="I5">
         <v>2</v>
       </c>
       <c r="L5" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="M5" t="s">
-        <v>20</v>
+        <v>129</v>
       </c>
       <c r="N5" t="s">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="O5" t="s">
-        <v>31</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.4">
@@ -1219,22 +1441,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="E6">
-        <v>18300</v>
+        <v>34450</v>
       </c>
       <c r="G6" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
       <c r="H6">
-        <v>55579837623</v>
+        <v>89589669476</v>
       </c>
       <c r="I6">
         <v>2</v>
@@ -1243,13 +1465,13 @@
         <v>19</v>
       </c>
       <c r="M6" t="s">
-        <v>20</v>
+        <v>122</v>
       </c>
       <c r="N6" t="s">
-        <v>30</v>
+        <v>123</v>
       </c>
       <c r="O6" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.4">
@@ -1257,22 +1479,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="E7">
-        <v>34400</v>
+        <v>37120</v>
       </c>
       <c r="G7" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="H7">
-        <v>55579825410</v>
+        <v>89589669206</v>
       </c>
       <c r="I7">
         <v>2</v>
@@ -1281,13 +1503,13 @@
         <v>19</v>
       </c>
       <c r="M7" t="s">
-        <v>20</v>
+        <v>122</v>
       </c>
       <c r="N7" t="s">
-        <v>30</v>
+        <v>123</v>
       </c>
       <c r="O7" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.4">
@@ -1295,22 +1517,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>138</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>139</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="E8">
-        <v>34700</v>
+        <v>24960</v>
       </c>
       <c r="G8" t="s">
-        <v>18</v>
+        <v>141</v>
       </c>
       <c r="H8">
-        <v>55579797058</v>
+        <v>89589668620</v>
       </c>
       <c r="I8">
         <v>2</v>
@@ -1319,13 +1541,13 @@
         <v>19</v>
       </c>
       <c r="M8" t="s">
-        <v>20</v>
+        <v>142</v>
       </c>
       <c r="N8" t="s">
-        <v>30</v>
+        <v>143</v>
       </c>
       <c r="O8" t="s">
-        <v>31</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.4">
@@ -1333,37 +1555,34 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>147</v>
       </c>
       <c r="E9">
-        <v>70100</v>
+        <v>13200</v>
       </c>
       <c r="G9" t="s">
-        <v>18</v>
+        <v>148</v>
       </c>
       <c r="H9">
-        <v>55579793345</v>
+        <v>89589668612</v>
       </c>
       <c r="I9">
         <v>2</v>
       </c>
       <c r="L9" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="M9" t="s">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="N9" t="s">
-        <v>30</v>
-      </c>
-      <c r="O9" t="s">
-        <v>31</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.4">
@@ -1371,22 +1590,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>152</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>153</v>
       </c>
       <c r="E10">
-        <v>34400</v>
+        <v>49100</v>
       </c>
       <c r="G10" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="H10">
-        <v>55579791835</v>
+        <v>89589668587</v>
       </c>
       <c r="I10">
         <v>2</v>
@@ -1395,13 +1614,13 @@
         <v>19</v>
       </c>
       <c r="M10" t="s">
-        <v>20</v>
+        <v>122</v>
       </c>
       <c r="N10" t="s">
-        <v>30</v>
+        <v>123</v>
       </c>
       <c r="O10" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.4">
@@ -1409,40 +1628,37 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>154</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
+        <v>156</v>
       </c>
       <c r="E11">
-        <v>20300</v>
+        <v>373990</v>
       </c>
       <c r="G11" t="s">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="H11">
-        <v>89588574489</v>
+        <v>89589668350</v>
       </c>
       <c r="I11">
         <v>2</v>
       </c>
-      <c r="J11" t="s">
-        <v>32</v>
-      </c>
-      <c r="K11" t="s">
-        <v>32</v>
-      </c>
       <c r="L11" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="M11" t="s">
-        <v>20</v>
+        <v>158</v>
       </c>
       <c r="N11" t="s">
-        <v>98</v>
+        <v>159</v>
+      </c>
+      <c r="O11" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.4">
@@ -1450,37 +1666,37 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>161</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>162</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>163</v>
       </c>
       <c r="E12">
-        <v>6940</v>
+        <v>12890</v>
       </c>
       <c r="G12" t="s">
-        <v>73</v>
+        <v>164</v>
       </c>
       <c r="H12">
-        <v>89588558835</v>
+        <v>89589668243</v>
       </c>
       <c r="I12">
         <v>2</v>
       </c>
       <c r="L12" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="M12" t="s">
-        <v>20</v>
+        <v>165</v>
       </c>
       <c r="N12" t="s">
-        <v>30</v>
+        <v>166</v>
       </c>
       <c r="O12" t="s">
-        <v>31</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.4">
@@ -1488,43 +1704,34 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>168</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>169</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>170</v>
       </c>
       <c r="E13">
-        <v>67400</v>
+        <v>19330</v>
       </c>
       <c r="G13" t="s">
-        <v>36</v>
+        <v>171</v>
       </c>
       <c r="H13">
-        <v>89588431148</v>
+        <v>89589668187</v>
       </c>
       <c r="I13">
         <v>2</v>
       </c>
-      <c r="J13" t="s">
-        <v>32</v>
-      </c>
-      <c r="K13" t="s">
-        <v>32</v>
-      </c>
       <c r="L13" t="s">
-        <v>19</v>
+        <v>108</v>
       </c>
       <c r="M13" t="s">
-        <v>20</v>
+        <v>109</v>
       </c>
       <c r="N13" t="s">
-        <v>37</v>
-      </c>
-      <c r="O13" t="s">
-        <v>38</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.4">
@@ -1532,22 +1739,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>172</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>173</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>174</v>
       </c>
       <c r="E14">
-        <v>72000</v>
+        <v>44940</v>
       </c>
       <c r="G14" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
       <c r="H14">
-        <v>55579432858</v>
+        <v>89589668088</v>
       </c>
       <c r="I14">
         <v>2</v>
@@ -1556,13 +1763,13 @@
         <v>19</v>
       </c>
       <c r="M14" t="s">
-        <v>20</v>
+        <v>122</v>
       </c>
       <c r="N14" t="s">
-        <v>30</v>
+        <v>123</v>
       </c>
       <c r="O14" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.4">
@@ -1570,37 +1777,37 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>175</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>176</v>
       </c>
       <c r="D15" t="s">
-        <v>43</v>
+        <v>177</v>
       </c>
       <c r="E15">
-        <v>64080</v>
+        <v>14810</v>
       </c>
       <c r="G15" t="s">
-        <v>44</v>
+        <v>178</v>
       </c>
       <c r="H15">
-        <v>55579386777</v>
+        <v>89589668101</v>
       </c>
       <c r="I15">
         <v>2</v>
       </c>
       <c r="L15" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="M15" t="s">
-        <v>20</v>
+        <v>158</v>
       </c>
       <c r="N15" t="s">
-        <v>30</v>
+        <v>179</v>
       </c>
       <c r="O15" t="s">
-        <v>31</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.4">
@@ -1608,22 +1815,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>181</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>182</v>
       </c>
       <c r="D16" t="s">
-        <v>47</v>
+        <v>183</v>
       </c>
       <c r="E16">
-        <v>4920</v>
+        <v>37120</v>
       </c>
       <c r="G16" t="s">
-        <v>48</v>
+        <v>121</v>
       </c>
       <c r="H16">
-        <v>89588140982</v>
+        <v>89589667648</v>
       </c>
       <c r="I16">
         <v>2</v>
@@ -1632,209 +1839,13 @@
         <v>19</v>
       </c>
       <c r="M16" t="s">
-        <v>20</v>
+        <v>122</v>
       </c>
       <c r="N16" t="s">
-        <v>30</v>
+        <v>123</v>
       </c>
       <c r="O16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17">
-        <v>11490</v>
-      </c>
-      <c r="G17" t="s">
-        <v>52</v>
-      </c>
-      <c r="H17">
-        <v>89588344122</v>
-      </c>
-      <c r="I17">
-        <v>2</v>
-      </c>
-      <c r="L17" t="s">
-        <v>19</v>
-      </c>
-      <c r="M17" t="s">
-        <v>20</v>
-      </c>
-      <c r="N17" t="s">
-        <v>30</v>
-      </c>
-      <c r="O17" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" t="s">
-        <v>55</v>
-      </c>
-      <c r="E18">
-        <v>3360</v>
-      </c>
-      <c r="G18" t="s">
-        <v>48</v>
-      </c>
-      <c r="H18">
-        <v>89588315934</v>
-      </c>
-      <c r="I18">
-        <v>2</v>
-      </c>
-      <c r="L18" t="s">
-        <v>19</v>
-      </c>
-      <c r="M18" t="s">
-        <v>20</v>
-      </c>
-      <c r="N18" t="s">
-        <v>30</v>
-      </c>
-      <c r="O18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>56</v>
-      </c>
-      <c r="C19" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" t="s">
-        <v>58</v>
-      </c>
-      <c r="E19">
-        <v>18170</v>
-      </c>
-      <c r="G19" t="s">
-        <v>59</v>
-      </c>
-      <c r="H19">
-        <v>89588305117</v>
-      </c>
-      <c r="I19">
-        <v>2</v>
-      </c>
-      <c r="J19" t="s">
-        <v>32</v>
-      </c>
-      <c r="K19" t="s">
-        <v>32</v>
-      </c>
-      <c r="L19" t="s">
-        <v>19</v>
-      </c>
-      <c r="M19" t="s">
-        <v>20</v>
-      </c>
-      <c r="N19" t="s">
-        <v>21</v>
-      </c>
-      <c r="O19" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" t="s">
-        <v>61</v>
-      </c>
-      <c r="E20">
-        <v>11780</v>
-      </c>
-      <c r="G20" t="s">
-        <v>59</v>
-      </c>
-      <c r="H20">
-        <v>89588204658</v>
-      </c>
-      <c r="I20">
-        <v>2</v>
-      </c>
-      <c r="L20" t="s">
-        <v>19</v>
-      </c>
-      <c r="M20" t="s">
-        <v>20</v>
-      </c>
-      <c r="N20" t="s">
-        <v>30</v>
-      </c>
-      <c r="O20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" t="s">
-        <v>63</v>
-      </c>
-      <c r="D21" t="s">
-        <v>64</v>
-      </c>
-      <c r="E21">
-        <v>19610</v>
-      </c>
-      <c r="G21" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21">
-        <v>55579303499</v>
-      </c>
-      <c r="I21">
-        <v>2</v>
-      </c>
-      <c r="L21" t="s">
-        <v>19</v>
-      </c>
-      <c r="M21" t="s">
-        <v>20</v>
-      </c>
-      <c r="N21" t="s">
-        <v>30</v>
-      </c>
-      <c r="O21" t="s">
-        <v>65</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -1844,7 +1855,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{594CDC67-64A4-4805-9B59-BA07E341B8C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B530DA9-6395-42D1-809B-F1F7D5490E34}">
   <dimension ref="A1:O21"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1900,22 +1911,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="E2">
-        <v>34700</v>
+        <v>10990</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H2">
-        <v>55579876708</v>
+        <v>55580027908</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -1938,22 +1949,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E3">
-        <v>69400</v>
+        <v>34700</v>
       </c>
       <c r="G3" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="H3">
-        <v>55579859939</v>
+        <v>55579876708</v>
       </c>
       <c r="I3">
         <v>2</v>
@@ -1976,22 +1987,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E4">
-        <v>18200</v>
+        <v>69400</v>
       </c>
       <c r="G4" t="s">
         <v>44</v>
       </c>
       <c r="H4">
-        <v>55579843217</v>
+        <v>55579859939</v>
       </c>
       <c r="I4">
         <v>2</v>
@@ -2014,22 +2025,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E5">
-        <v>18300</v>
+        <v>18200</v>
       </c>
       <c r="G5" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="H5">
-        <v>55579837623</v>
+        <v>55579843217</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -2052,22 +2063,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E6">
-        <v>34400</v>
+        <v>18300</v>
       </c>
       <c r="G6" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="H6">
-        <v>55579825410</v>
+        <v>55579837623</v>
       </c>
       <c r="I6">
         <v>2</v>
@@ -2090,22 +2101,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E7">
-        <v>34700</v>
+        <v>34400</v>
       </c>
       <c r="G7" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="H7">
-        <v>55579797058</v>
+        <v>55579825410</v>
       </c>
       <c r="I7">
         <v>2</v>
@@ -2128,22 +2139,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E8">
-        <v>70100</v>
+        <v>34700</v>
       </c>
       <c r="G8" t="s">
         <v>18</v>
       </c>
       <c r="H8">
-        <v>55579793345</v>
+        <v>55579797058</v>
       </c>
       <c r="I8">
         <v>2</v>
@@ -2166,22 +2177,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E9">
-        <v>34400</v>
+        <v>70100</v>
       </c>
       <c r="G9" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="H9">
-        <v>55579791835</v>
+        <v>55579793345</v>
       </c>
       <c r="I9">
         <v>2</v>
@@ -2204,31 +2215,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="E10">
-        <v>20300</v>
+        <v>34400</v>
       </c>
       <c r="G10" t="s">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="H10">
-        <v>89588574489</v>
+        <v>55579791835</v>
       </c>
       <c r="I10">
         <v>2</v>
-      </c>
-      <c r="J10" t="s">
-        <v>32</v>
-      </c>
-      <c r="K10" t="s">
-        <v>32</v>
       </c>
       <c r="L10" t="s">
         <v>19</v>
@@ -2237,7 +2242,10 @@
         <v>20</v>
       </c>
       <c r="N10" t="s">
-        <v>98</v>
+        <v>30</v>
+      </c>
+      <c r="O10" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.4">
@@ -2245,25 +2253,31 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="E11">
-        <v>6940</v>
+        <v>20300</v>
       </c>
       <c r="G11" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="H11">
-        <v>89588558835</v>
+        <v>89588574489</v>
       </c>
       <c r="I11">
         <v>2</v>
+      </c>
+      <c r="J11" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" t="s">
+        <v>32</v>
       </c>
       <c r="L11" t="s">
         <v>19</v>
@@ -2272,10 +2286,7 @@
         <v>20</v>
       </c>
       <c r="N11" t="s">
-        <v>30</v>
-      </c>
-      <c r="O11" t="s">
-        <v>31</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.4">
@@ -2283,31 +2294,25 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="E12">
-        <v>67400</v>
+        <v>6940</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="H12">
-        <v>89588431148</v>
+        <v>89588558835</v>
       </c>
       <c r="I12">
         <v>2</v>
-      </c>
-      <c r="J12" t="s">
-        <v>32</v>
-      </c>
-      <c r="K12" t="s">
-        <v>32</v>
       </c>
       <c r="L12" t="s">
         <v>19</v>
@@ -2316,10 +2321,10 @@
         <v>20</v>
       </c>
       <c r="N12" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="O12" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.4">
@@ -2327,25 +2332,31 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E13">
-        <v>72000</v>
+        <v>67400</v>
       </c>
       <c r="G13" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H13">
-        <v>55579432858</v>
+        <v>89588431148</v>
       </c>
       <c r="I13">
         <v>2</v>
+      </c>
+      <c r="J13" t="s">
+        <v>32</v>
+      </c>
+      <c r="K13" t="s">
+        <v>32</v>
       </c>
       <c r="L13" t="s">
         <v>19</v>
@@ -2354,10 +2365,10 @@
         <v>20</v>
       </c>
       <c r="N13" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="O13" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.4">
@@ -2368,19 +2379,19 @@
         <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E14">
-        <v>64080</v>
+        <v>72000</v>
       </c>
       <c r="G14" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="H14">
-        <v>55579386777</v>
+        <v>55579432858</v>
       </c>
       <c r="I14">
         <v>2</v>
@@ -2403,22 +2414,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E15">
-        <v>4920</v>
+        <v>64080</v>
       </c>
       <c r="G15" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H15">
-        <v>89588140982</v>
+        <v>55579386777</v>
       </c>
       <c r="I15">
         <v>2</v>
@@ -2441,22 +2452,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D16" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E16">
-        <v>11490</v>
+        <v>4920</v>
       </c>
       <c r="G16" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H16">
-        <v>89588344122</v>
+        <v>89588140982</v>
       </c>
       <c r="I16">
         <v>2</v>
@@ -2479,22 +2490,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E17">
-        <v>3360</v>
+        <v>11490</v>
       </c>
       <c r="G17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H17">
-        <v>89588315934</v>
+        <v>89588344122</v>
       </c>
       <c r="I17">
         <v>2</v>
@@ -2517,31 +2528,25 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E18">
-        <v>18170</v>
+        <v>3360</v>
       </c>
       <c r="G18" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="H18">
-        <v>89588305117</v>
+        <v>89588315934</v>
       </c>
       <c r="I18">
         <v>2</v>
-      </c>
-      <c r="J18" t="s">
-        <v>32</v>
-      </c>
-      <c r="K18" t="s">
-        <v>32</v>
       </c>
       <c r="L18" t="s">
         <v>19</v>
@@ -2550,10 +2555,10 @@
         <v>20</v>
       </c>
       <c r="N18" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="O18" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.4">
@@ -2561,25 +2566,31 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E19">
-        <v>11780</v>
+        <v>18170</v>
       </c>
       <c r="G19" t="s">
         <v>59</v>
       </c>
       <c r="H19">
-        <v>89588204658</v>
+        <v>89588305117</v>
       </c>
       <c r="I19">
         <v>2</v>
+      </c>
+      <c r="J19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K19" t="s">
+        <v>32</v>
       </c>
       <c r="L19" t="s">
         <v>19</v>
@@ -2588,10 +2599,10 @@
         <v>20</v>
       </c>
       <c r="N19" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="O19" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.4">
@@ -2599,22 +2610,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E20">
-        <v>19610</v>
+        <v>11780</v>
       </c>
       <c r="G20" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="H20">
-        <v>55579303499</v>
+        <v>89588204658</v>
       </c>
       <c r="I20">
         <v>2</v>
@@ -2629,7 +2640,7 @@
         <v>30</v>
       </c>
       <c r="O20" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.4">
@@ -2637,28 +2648,25 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C21" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E21">
-        <v>44160</v>
+        <v>19610</v>
       </c>
       <c r="G21" t="s">
         <v>23</v>
       </c>
       <c r="H21">
-        <v>55579294213</v>
+        <v>55579303499</v>
       </c>
       <c r="I21">
         <v>2</v>
-      </c>
-      <c r="J21" t="s">
-        <v>69</v>
       </c>
       <c r="L21" t="s">
         <v>19</v>
@@ -2670,7 +2678,7 @@
         <v>30</v>
       </c>
       <c r="O21" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
